--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486420_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486420_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0555</v>
+        <v>7.2231</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1111</v>
+        <v>5.217</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9444</v>
+        <v>2.0061</v>
       </c>
       <c r="G2" t="n">
         <v>4.2948</v>
@@ -610,13 +610,13 @@
         <v>3.6976</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1082</v>
+        <v>0.2758</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6548</v>
+        <v>0.7607</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5465</v>
+        <v>-0.4849</v>
       </c>
       <c r="V2" t="n">
         <v>1.13</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2213</v>
+        <v>3.0721</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7051</v>
+        <v>2.5559</v>
       </c>
       <c r="F3" t="n">
         <v>0.5163</v>
@@ -688,10 +688,10 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8446</v>
+        <v>-0.9938</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7294</v>
+        <v>0.1214</v>
       </c>
       <c r="U3" t="n">
         <v>-1.1152</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0634</v>
+        <v>3.0075</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8173</v>
+        <v>1.8232</v>
       </c>
       <c r="F4" t="n">
-        <v>1.246</v>
+        <v>1.1844</v>
       </c>
       <c r="G4" t="n">
         <v>1.1323</v>
@@ -766,13 +766,13 @@
         <v>3.9151</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2212</v>
+        <v>-0.277</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5684</v>
+        <v>0.4374</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6528</v>
+        <v>-0.7144</v>
       </c>
       <c r="V4" t="n">
         <v>1.4997</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4764</v>
+        <v>0.5034</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9713</v>
+        <v>-1.636</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4477</v>
+        <v>2.1395</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4875</v>
@@ -844,13 +844,13 @@
         <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2536</v>
+        <v>-0.2265</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5239</v>
+        <v>-0.1887</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2704</v>
+        <v>-0.0379</v>
       </c>
       <c r="V5" t="n">
         <v>1.13</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3575</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1157</v>
+        <v>1.4019</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7582</v>
+        <v>-1.974</v>
       </c>
       <c r="G6" t="n">
         <v>1.0936</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4161</v>
+        <v>-0.5134</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2281</v>
+        <v>0.5143</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-1.0278</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9347</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BOCCA</t>
+          <t>O. MATULIONIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3887</v>
+        <v>-0.618</v>
       </c>
       <c r="E7" t="n">
-        <v>0.488</v>
+        <v>-0.8949</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8767</v>
+        <v>0.2769</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.177</v>
+        <v>-1.2504</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.542</v>
+        <v>-0.4169</v>
       </c>
       <c r="I7" t="n">
-        <v>1.365</v>
+        <v>-0.8335</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0071</v>
+        <v>-0.1282</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5626</v>
+        <v>-0.0151</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5554</v>
+        <v>-0.1131</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1698</v>
+        <v>-1.1222</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9794</v>
+        <v>-0.4018</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8096</v>
+        <v>-0.7204</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1336</v>
+        <v>-0.6726</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4951</v>
+        <v>0.3209</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3615</v>
+        <v>-0.9935</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.0854</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.0854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>J. BOCCA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4857</v>
+        <v>-0.6623</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5556</v>
+        <v>0.1527</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0413</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6848</v>
+        <v>-0.177</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6545</v>
+        <v>-1.542</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0303</v>
+        <v>1.365</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.616</v>
+        <v>-0.0071</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5411</v>
+        <v>-0.5626</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0.5554</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0688</v>
+        <v>-0.1698</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1134</v>
+        <v>-0.9794</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0446</v>
+        <v>0.8096</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2415</v>
+        <v>-0.14</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1717</v>
+        <v>0.1598</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9301</v>
+        <v>-0.2998</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.0854</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.0854</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. MATULIONIS</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.014</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0751</v>
+        <v>0.2889</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0611</v>
+        <v>-1.0413</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2504</v>
+        <v>-1.6848</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4169</v>
+        <v>-1.6545</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8335</v>
+        <v>-0.0303</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1282</v>
+        <v>-0.616</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0151</v>
+        <v>-0.5411</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1131</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1222</v>
+        <v>-1.0688</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4018</v>
+        <v>-1.1134</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7204</v>
+        <v>0.0446</v>
       </c>
       <c r="P9" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3926</v>
+        <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0687</v>
+        <v>-0.0252</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1406</v>
+        <v>0.9049</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2093</v>
+        <v>-0.9301</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6055</v>
+        <v>-1.3212</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5773</v>
+        <v>1.6458</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1828</v>
+        <v>-2.9671</v>
       </c>
       <c r="G10" t="n">
         <v>1.4251</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3356</v>
+        <v>-0.0514</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5756</v>
+        <v>0.6441</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9113</v>
+        <v>-0.6955</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2599</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6357</v>
+        <v>-1.4931</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7278</v>
+        <v>-1.6161</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0921</v>
+        <v>0.1229</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4197</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.781</v>
+        <v>-0.6384</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2055</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5755</v>
+        <v>-0.5447</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.044499999999999</v>
+        <v>8.386899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>8.5959</v>
+        <v>8.9384</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5513999999999991</v>
+        <v>-0.5512999999999995</v>
       </c>
       <c r="G12" t="n">
         <v>4.992300000000001</v>
@@ -1390,10 +1390,10 @@
         <v>20.6632</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.6053</v>
+        <v>-3.2625</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2387</v>
+        <v>3.5811</v>
       </c>
       <c r="U12" t="n">
         <v>-6.8438</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5416</v>
+        <v>3.6322</v>
       </c>
       <c r="E13" t="n">
-        <v>4.547</v>
+        <v>3.6529</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0054</v>
+        <v>-0.0208</v>
       </c>
       <c r="G13" t="n">
         <v>5.5928</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6013</v>
+        <v>0.6919</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3447</v>
+        <v>0.4506</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2565</v>
+        <v>0.2412</v>
       </c>
       <c r="V13" t="n">
         <v>-1.13</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4046</v>
+        <v>3.6274</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1806</v>
+        <v>3.9513</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.776</v>
+        <v>-0.3239</v>
       </c>
       <c r="G14" t="n">
         <v>0.1455</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6289</v>
+        <v>0.8517</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4563</v>
+        <v>1.2269</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8274</v>
+        <v>-0.3752</v>
       </c>
       <c r="V14" t="n">
         <v>1.3252</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. DEBAUT</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4459</v>
+        <v>0.4835</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3397</v>
+        <v>0.2972</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7856</v>
+        <v>0.1863</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0265</v>
+        <v>-1.4095</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9548</v>
+        <v>-0.435</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9283</v>
+        <v>-0.9745</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4772</v>
+        <v>-0.2412</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.173</v>
+        <v>-0.0516</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6502</v>
+        <v>-0.1896</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5038</v>
+        <v>-1.1683</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7819</v>
+        <v>-0.3834</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2781</v>
+        <v>-0.7849</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.6101</v>
+        <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6475</v>
+        <v>1.0229</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2281</v>
+        <v>0.7559</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4194</v>
+        <v>0.2671</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BERGSTEDT</t>
+          <t>M. CAICEDO SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0257</v>
+        <v>0.4247</v>
       </c>
       <c r="E16" t="n">
-        <v>1.539</v>
+        <v>1.2443</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5646</v>
+        <v>-0.8196</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3545</v>
+        <v>-0.5147</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2615</v>
+        <v>1.6393</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.616</v>
+        <v>-2.1539</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3285</v>
+        <v>1.853</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3285</v>
+        <v>2.5216</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.6686</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6829</v>
+        <v>-2.3677</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.067</v>
+        <v>-0.8823</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.616</v>
+        <v>-1.4854</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2175</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1113</v>
+        <v>0.9617</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0805</v>
+        <v>0.7186</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0308</v>
+        <v>0.243</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>L. DEBAUT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1677</v>
+        <v>0.175</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5019</v>
+        <v>-0.4515</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6696</v>
+        <v>0.6264</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3405</v>
+        <v>-0.0265</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.362</v>
+        <v>-0.9548</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9785</v>
+        <v>0.9283</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7086</v>
+        <v>0.4772</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0365</v>
+        <v>-0.173</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7451</v>
+        <v>0.6502</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.632</v>
+        <v>-0.5038</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3985</v>
+        <v>-0.7819</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2335</v>
+        <v>0.2781</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2175</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.6101</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0205</v>
+        <v>1.3765</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0805</v>
+        <v>1.1164</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.06</v>
+        <v>0.2602</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9347</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. CAICEDO SANCHEZ</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1893</v>
+        <v>0.0866</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0208</v>
+        <v>0.7254</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2101</v>
+        <v>-0.6388</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5147</v>
+        <v>-1.3405</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6393</v>
+        <v>-0.362</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.1539</v>
+        <v>-0.9785</v>
       </c>
       <c r="J18" t="n">
-        <v>1.853</v>
+        <v>-0.7086</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5216</v>
+        <v>0.0365</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6686</v>
+        <v>-0.7451</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3677</v>
+        <v>-0.632</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8823</v>
+        <v>-0.3985</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4854</v>
+        <v>-0.2335</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2175</v>
+        <v>0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3476</v>
+        <v>0.2749</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4951</v>
+        <v>0.304</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1475</v>
+        <v>-0.0291</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1952</v>
+        <v>0.9347</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>J. BERGSTEDT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7638</v>
+        <v>-0.0372</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7087</v>
+        <v>1.6507</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0552</v>
+        <v>-1.6879</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4095</v>
+        <v>-0.3545</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.435</v>
+        <v>0.2615</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9745</v>
+        <v>-0.616</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2412</v>
+        <v>0.3285</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0516</v>
+        <v>0.3285</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1896</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1683</v>
+        <v>-0.6829</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3834</v>
+        <v>-0.067</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7849</v>
+        <v>-0.616</v>
       </c>
       <c r="P19" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2244</v>
+        <v>0.0997</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2499</v>
+        <v>0.1923</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0256</v>
+        <v>-0.0925</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>S. RODRIGUEZ FEBLES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6781</v>
+        <v>-1.4224</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0925</v>
+        <v>-0.4485</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7706</v>
+        <v>-0.9739</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9982</v>
+        <v>-0.4778</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3863</v>
+        <v>-1.3838</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.612</v>
+        <v>0.906</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2005</v>
+        <v>1.14</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6451</v>
+        <v>-0.4864</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5554</v>
+        <v>1.6264</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1987</v>
+        <v>-1.6178</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0313</v>
+        <v>-0.8974</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1674</v>
+        <v>-0.7204</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.305</v>
+        <v>-3.4801</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7020999999999999</v>
+        <v>0.9052</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1971</v>
+        <v>0.9361</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8992</v>
+        <v>-0.031</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1952</v>
+        <v>0.7602</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X20" t="n">
         <v>-0.1952</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ FEBLES</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8874</v>
+        <v>-1.4996</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6721</v>
+        <v>-0.2427</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2154</v>
+        <v>-1.2569</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4778</v>
+        <v>-0.9982</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3838</v>
+        <v>-0.3863</v>
       </c>
       <c r="I21" t="n">
-        <v>0.906</v>
+        <v>-0.612</v>
       </c>
       <c r="J21" t="n">
-        <v>1.14</v>
+        <v>1.2005</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4864</v>
+        <v>0.6451</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6264</v>
+        <v>0.5554</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6178</v>
+        <v>-2.1987</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8974</v>
+        <v>-1.0313</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7204</v>
+        <v>-1.1674</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.6101</v>
+        <v>0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4801</v>
+        <v>-1.305</v>
       </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4402</v>
+        <v>-0.5236</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7126</v>
+        <v>-0.1382</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2724</v>
+        <v>-0.3854</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7602</v>
+        <v>-0.1952</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>-0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8104</v>
+        <v>-2.7525</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8461</v>
+        <v>-1.9578</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9643</v>
+        <v>-0.7947</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3909</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>0.363</v>
+        <v>0.4209</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4146</v>
+        <v>0.3028</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0516</v>
+        <v>0.1181</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5649999999999999</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. EZQUERRA TRELLES</t>
+          <t>N. HOOVER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2503</v>
+        <v>-3.8541</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0521</v>
+        <v>-3.9297</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1983</v>
+        <v>0.0756</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4448</v>
+        <v>-2.7733</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6384</v>
+        <v>-1.539</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1936</v>
+        <v>-1.2343</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.173</v>
+        <v>-2.5627</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.173</v>
+        <v>-0.9212</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.6415</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2718</v>
+        <v>-0.2106</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4654</v>
+        <v>-0.6178</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1936</v>
+        <v>0.4072</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.1326</v>
+        <v>-0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5676</v>
+        <v>-1.7401</v>
       </c>
       <c r="R23" t="n">
-        <v>0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3271</v>
+        <v>-0.146</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6886</v>
+        <v>0.1779</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3615</v>
+        <v>-0.3239</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. HOOVER</t>
+          <t>J. EZQUERRA TRELLES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6639</v>
+        <v>-3.9279</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.712</v>
+        <v>-3.9403</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9519</v>
+        <v>0.0124</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.7733</v>
+        <v>-0.4448</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.539</v>
+        <v>-0.6384</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2343</v>
+        <v>0.1936</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.5627</v>
+        <v>-0.173</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9212</v>
+        <v>-0.173</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.6415</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2106</v>
+        <v>-0.2718</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6178</v>
+        <v>-0.4654</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4072</v>
+        <v>0.1936</v>
       </c>
       <c r="P24" t="n">
-        <v>-0</v>
+        <v>-4.1326</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.7401</v>
+        <v>-4.5676</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9559</v>
+        <v>0.6495</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6044</v>
+        <v>0.8003</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3514</v>
+        <v>-0.1508</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9347</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.044499999999999</v>
+        <v>-5.064299999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.551099999999999</v>
+        <v>0.5512999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.595799999999999</v>
+        <v>-5.615799999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.9924</v>
+        <v>-4.992399999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-3.33066907387547e-16</v>
       </c>
       <c r="I25" t="n">
         <v>-4.9924</v>
@@ -2380,7 +2380,7 @@
         <v>8.874600000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>7.408300000000001</v>
+        <v>7.4083</v>
       </c>
       <c r="L25" t="n">
         <v>1.4663</v>
@@ -2389,7 +2389,7 @@
         <v>-13.8672</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.4084</v>
+        <v>-7.408399999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-6.4588</v>
@@ -2404,16 +2404,16 @@
         <v>13.0502</v>
       </c>
       <c r="S25" t="n">
-        <v>3.605</v>
+        <v>6.585299999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>6.843800000000001</v>
+        <v>6.8436</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.2387</v>
+        <v>-0.2583000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9553999999999999</v>
+        <v>0.9554000000000004</v>
       </c>
       <c r="W25" t="n">
         <v>5.496</v>
